--- a/examples/Financial-Summary-test.xlsx
+++ b/examples/Financial-Summary-test.xlsx
@@ -261,7 +261,7 @@
     <ext cx="5400000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
+        <cNvPr id="1" name="Chart 1" title="Chart"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>

--- a/examples/Financial-Summary-test.xlsx
+++ b/examples/Financial-Summary-test.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0)"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +30,13 @@
     <font>
       <name val="Calibri"/>
       <color rgb="FFAAAAAA"/>
-      <sz val="10"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -152,7 +161,7 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Sheet1'!$B$3:$B$5</f>
+              <f>'Sheet1'!$B$3:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -171,7 +180,7 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Sheet1'!$C$3:$C$5</f>
+              <f>'Sheet1'!$C$3:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -190,7 +199,7 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Sheet1'!$D$3:$D$5</f>
+              <f>'Sheet1'!$D$3:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -209,7 +218,7 @@
           </spPr>
           <val>
             <numRef>
-              <f>'Sheet1'!$E$3:$E$5</f>
+              <f>'Sheet1'!$E$3:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -565,13 +574,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q1-Q4 FINANCIAL OVERVIEW</t>
+          <t>Q1-Q4 DEPARTMENTAL FINANCIAL OVERVIEW</t>
         </is>
       </c>
     </row>
@@ -669,8 +678,30 @@
       <c r="E5" t="n">
         <v>90000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="2" t="n">
         <v>337000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>95000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>115000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>130000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>450000</v>
       </c>
     </row>
   </sheetData>

--- a/examples/Financial-Summary-test.xlsx
+++ b/examples/Financial-Summary-test.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0)"/>
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]#,##0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -59,10 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -270,7 +272,7 @@
     <ext cx="5400000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1" title="Chart"/>
+        <cNvPr id="1" name="Chart 1"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
@@ -283,6 +285,19 @@
     <clientData/>
   </oneCellAnchor>
 </wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DeptRevenueTableTest" displayName="DeptRevenueTableTest" ref="A2:F6" headerRowCount="0">
+  <tableColumns count="6">
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4"/>
+    <tableColumn id="5" name="Column5"/>
+    <tableColumn id="6" name="Column6"/>
+  </tableColumns>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,16 +671,11 @@
       <c r="E4" t="n">
         <v>60000</v>
       </c>
-      <c r="F4" t="n">
-        <v>207000</v>
+      <c r="F4" s="2" t="n">
+        <v>-15000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
       <c r="B5" t="n">
         <v>80000</v>
       </c>
@@ -678,7 +688,7 @@
       <c r="E5" t="n">
         <v>90000</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" t="n">
         <v>337000</v>
       </c>
     </row>
@@ -700,15 +710,40 @@
       <c r="E6" t="n">
         <v>130000</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>450000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Supplementary reference notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/examples/Financial-Summary-test.xlsx
+++ b/examples/Financial-Summary-test.xlsx
@@ -287,19 +287,6 @@
 </wsDr>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DeptRevenueTableTest" displayName="DeptRevenueTableTest" ref="A2:F6" headerRowCount="0">
-  <tableColumns count="6">
-    <tableColumn id="1" name="Column1"/>
-    <tableColumn id="2" name="Column2"/>
-    <tableColumn id="3" name="Column3"/>
-    <tableColumn id="4" name="Column4"/>
-    <tableColumn id="5" name="Column5"/>
-    <tableColumn id="6" name="Column6"/>
-  </tableColumns>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -589,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,6 +663,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="B5" t="n">
         <v>80000</v>
       </c>
@@ -714,16 +706,20 @@
         <v>450000</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Confidential - Internal Management Reporting Only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
